--- a/deliverables/FA26SE115_Report5_Test Report.xlsx
+++ b/deliverables/FA26SE115_Report5_Test Report.xlsx
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E11" s="140" t="inlineStr">
         <is>
-          <t>Rounds 1-1 of 58 system test cases on the local stack</t>
+          <t>Rounds 1-3 of 58 system test cases on the local stack</t>
         </is>
       </c>
       <c r="F11" s="141" t="inlineStr">
@@ -3024,12 +3024,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -3100,12 +3120,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>200/200/200, count=0</t>
@@ -3649,12 +3689,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -3701,12 +3761,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 403</t>
@@ -3776,15 +3856,35 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>usage 200, dataset 200. Defect DEF-01: a Platform Admin who is not a member opens the dataset (HTTP 200). Code: ProjectAccess.can_read_raw_data returns True for is_admin (projects/service.py). Report III BR-06 / UC-02 says the admin sees metadata only.</t>
+          <t>usage 200, dataset 200</t>
         </is>
       </c>
       <c r="Q15" s="41" t="n"/>
@@ -3850,12 +3950,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="42" t="n"/>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="42" t="n"/>
-      <c r="N17" s="42" t="n"/>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L17" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
           <t>200/200</t>
@@ -5028,7 +5148,7 @@
       </c>
       <c r="C6" s="107" t="inlineStr">
         <is>
-          <t>Figures of round 1 on the local stack. Research Run cases that need an LLM provider are Pending.</t>
+          <t>Figures of round 3 on the local stack. Research Run cases that need an LLM provider are Pending.</t>
         </is>
       </c>
       <c r="D6" s="150" t="n"/>
@@ -5114,19 +5234,19 @@
         <v/>
       </c>
       <c r="D11" s="71">
-        <f>'Authentication &amp; Account'!B6</f>
+        <f>'Authentication &amp; Account'!B8</f>
         <v/>
       </c>
       <c r="E11" s="71">
-        <f>'Authentication &amp; Account'!C6</f>
+        <f>'Authentication &amp; Account'!C8</f>
         <v/>
       </c>
       <c r="F11" s="71">
-        <f>'Authentication &amp; Account'!D6</f>
+        <f>'Authentication &amp; Account'!D8</f>
         <v/>
       </c>
       <c r="G11" s="71">
-        <f>'Authentication &amp; Account'!E6</f>
+        <f>'Authentication &amp; Account'!E8</f>
         <v/>
       </c>
       <c r="H11" s="73">
@@ -5144,19 +5264,19 @@
         <v/>
       </c>
       <c r="D12" s="71">
-        <f>'Project Workspace'!B6</f>
+        <f>'Project Workspace'!B8</f>
         <v/>
       </c>
       <c r="E12" s="71">
-        <f>'Project Workspace'!C6</f>
+        <f>'Project Workspace'!C8</f>
         <v/>
       </c>
       <c r="F12" s="71">
-        <f>'Project Workspace'!D6</f>
+        <f>'Project Workspace'!D8</f>
         <v/>
       </c>
       <c r="G12" s="71">
-        <f>'Project Workspace'!E6</f>
+        <f>'Project Workspace'!E8</f>
         <v/>
       </c>
       <c r="H12" s="73">
@@ -5174,19 +5294,19 @@
         <v/>
       </c>
       <c r="D13" s="71">
-        <f>'Data Management'!B6</f>
+        <f>'Data Management'!B8</f>
         <v/>
       </c>
       <c r="E13" s="71">
-        <f>'Data Management'!C6</f>
+        <f>'Data Management'!C8</f>
         <v/>
       </c>
       <c r="F13" s="71">
-        <f>'Data Management'!D6</f>
+        <f>'Data Management'!D8</f>
         <v/>
       </c>
       <c r="G13" s="71">
-        <f>'Data Management'!E6</f>
+        <f>'Data Management'!E8</f>
         <v/>
       </c>
       <c r="H13" s="73">
@@ -5204,19 +5324,19 @@
         <v/>
       </c>
       <c r="D14" s="71">
-        <f>'Data Connections &amp; Integrations'!B6</f>
+        <f>'Data Connections &amp; Integrations'!B8</f>
         <v/>
       </c>
       <c r="E14" s="71">
-        <f>'Data Connections &amp; Integrations'!C6</f>
+        <f>'Data Connections &amp; Integrations'!C8</f>
         <v/>
       </c>
       <c r="F14" s="71">
-        <f>'Data Connections &amp; Integrations'!D6</f>
+        <f>'Data Connections &amp; Integrations'!D8</f>
         <v/>
       </c>
       <c r="G14" s="71">
-        <f>'Data Connections &amp; Integrations'!E6</f>
+        <f>'Data Connections &amp; Integrations'!E8</f>
         <v/>
       </c>
       <c r="H14" s="73">
@@ -5234,19 +5354,19 @@
         <v/>
       </c>
       <c r="D15" s="71">
-        <f>'Local Node'!B6</f>
+        <f>'Local Node'!B8</f>
         <v/>
       </c>
       <c r="E15" s="71">
-        <f>'Local Node'!C6</f>
+        <f>'Local Node'!C8</f>
         <v/>
       </c>
       <c r="F15" s="71">
-        <f>'Local Node'!D6</f>
+        <f>'Local Node'!D8</f>
         <v/>
       </c>
       <c r="G15" s="71">
-        <f>'Local Node'!E6</f>
+        <f>'Local Node'!E8</f>
         <v/>
       </c>
       <c r="H15" s="73">
@@ -5264,19 +5384,19 @@
         <v/>
       </c>
       <c r="D16" s="71">
-        <f>'Research Run Orchestration'!B6</f>
+        <f>'Research Run Orchestration'!B8</f>
         <v/>
       </c>
       <c r="E16" s="71">
-        <f>'Research Run Orchestration'!C6</f>
+        <f>'Research Run Orchestration'!C8</f>
         <v/>
       </c>
       <c r="F16" s="71">
-        <f>'Research Run Orchestration'!D6</f>
+        <f>'Research Run Orchestration'!D8</f>
         <v/>
       </c>
       <c r="G16" s="71">
-        <f>'Research Run Orchestration'!E6</f>
+        <f>'Research Run Orchestration'!E8</f>
         <v/>
       </c>
       <c r="H16" s="73">
@@ -5294,19 +5414,19 @@
         <v/>
       </c>
       <c r="D17" s="71">
-        <f>'Notifications'!B6</f>
+        <f>'Notifications'!B8</f>
         <v/>
       </c>
       <c r="E17" s="71">
-        <f>'Notifications'!C6</f>
+        <f>'Notifications'!C8</f>
         <v/>
       </c>
       <c r="F17" s="71">
-        <f>'Notifications'!D6</f>
+        <f>'Notifications'!D8</f>
         <v/>
       </c>
       <c r="G17" s="71">
-        <f>'Notifications'!E6</f>
+        <f>'Notifications'!E8</f>
         <v/>
       </c>
       <c r="H17" s="73">
@@ -5323,19 +5443,19 @@
         <v/>
       </c>
       <c r="D18" s="71">
-        <f>'Administration'!B6</f>
+        <f>'Administration'!B8</f>
         <v/>
       </c>
       <c r="E18" s="71">
-        <f>'Administration'!C6</f>
+        <f>'Administration'!C8</f>
         <v/>
       </c>
       <c r="F18" s="71">
-        <f>'Administration'!D6</f>
+        <f>'Administration'!D8</f>
         <v/>
       </c>
       <c r="G18" s="71">
-        <f>'Administration'!E6</f>
+        <f>'Administration'!E8</f>
         <v/>
       </c>
       <c r="H18" s="73">
@@ -5859,12 +5979,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 200, code found in mail log</t>
@@ -5911,12 +6051,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 400</t>
@@ -5965,12 +6125,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>verify HTTP 200, me HTTP 200</t>
@@ -6017,12 +6197,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
           <t>HTTP 400</t>
@@ -6069,12 +6269,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="42" t="n"/>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
           <t>HTTP 403</t>
@@ -6143,12 +6363,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="42" t="n"/>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="42" t="n"/>
-      <c r="N18" s="42" t="n"/>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
           <t>HTTP 401</t>
@@ -6218,12 +6458,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I20" s="42" t="n"/>
-      <c r="J20" s="42" t="n"/>
-      <c r="K20" s="42" t="n"/>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="42" t="n"/>
-      <c r="N20" s="42" t="n"/>
+      <c r="I20" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J20" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K20" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L20" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M20" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N20" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -6292,12 +6552,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I22" s="42" t="n"/>
-      <c r="J22" s="42" t="n"/>
-      <c r="K22" s="42" t="n"/>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="42" t="n"/>
-      <c r="N22" s="42" t="n"/>
+      <c r="I22" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J22" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L22" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M22" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N22" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O22" s="42" t="inlineStr">
         <is>
           <t>logout HTTP 200, me HTTP 401</t>
@@ -6749,12 +7029,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 201</t>
@@ -6801,12 +7101,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 422</t>
@@ -6875,12 +7195,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
           <t>HTTP 200, 0 projects</t>
@@ -6927,12 +7267,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="42" t="n"/>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
           <t>HTTP 404</t>
@@ -7002,12 +7362,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="42" t="n"/>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="42" t="n"/>
-      <c r="N18" s="42" t="n"/>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
           <t>HTTP 201</t>
@@ -7054,12 +7434,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-      <c r="N19" s="42" t="n"/>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
           <t>HTTP 422</t>
@@ -7129,12 +7529,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="42" t="n"/>
-      <c r="K21" s="42" t="n"/>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="n"/>
-      <c r="N21" s="42" t="n"/>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L21" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O21" s="42" t="inlineStr">
         <is>
           <t>accept HTTP 200, project HTTP 200</t>
@@ -7202,12 +7622,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
-      <c r="N23" s="42" t="n"/>
+      <c r="I23" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J23" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K23" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L23" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M23" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N23" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O23" s="42" t="inlineStr">
         <is>
           <t>HTTP 200, version 0-&gt;1</t>
@@ -7253,12 +7693,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I24" s="42" t="n"/>
-      <c r="J24" s="42" t="n"/>
-      <c r="K24" s="42" t="n"/>
-      <c r="L24" s="42" t="n"/>
-      <c r="M24" s="42" t="n"/>
-      <c r="N24" s="42" t="n"/>
+      <c r="I24" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J24" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K24" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L24" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M24" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N24" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O24" s="42" t="inlineStr">
         <is>
           <t>HTTP 409</t>
@@ -7304,12 +7764,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I25" s="42" t="n"/>
-      <c r="J25" s="42" t="n"/>
-      <c r="K25" s="42" t="n"/>
-      <c r="L25" s="42" t="n"/>
-      <c r="M25" s="42" t="n"/>
-      <c r="N25" s="42" t="n"/>
+      <c r="I25" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J25" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K25" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L25" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M25" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N25" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O25" s="42" t="inlineStr">
         <is>
           <t>HTTP 403</t>
@@ -7376,12 +7856,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I27" s="42" t="n"/>
-      <c r="J27" s="42" t="n"/>
-      <c r="K27" s="42" t="n"/>
-      <c r="L27" s="42" t="n"/>
-      <c r="M27" s="42" t="n"/>
-      <c r="N27" s="42" t="n"/>
+      <c r="I27" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J27" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K27" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L27" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M27" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N27" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O27" s="42" t="inlineStr">
         <is>
           <t>HTTP 200, 4 entries</t>
@@ -7450,12 +7950,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I29" s="42" t="n"/>
-      <c r="J29" s="42" t="n"/>
-      <c r="K29" s="42" t="n"/>
-      <c r="L29" s="42" t="n"/>
-      <c r="M29" s="42" t="n"/>
-      <c r="N29" s="42" t="n"/>
+      <c r="I29" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J29" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K29" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L29" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M29" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N29" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O29" s="42" t="inlineStr">
         <is>
           <t>archive 200, patch 409, restore 200</t>
@@ -7522,12 +8042,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I31" s="42" t="n"/>
-      <c r="J31" s="42" t="n"/>
-      <c r="K31" s="42" t="n"/>
-      <c r="L31" s="42" t="n"/>
-      <c r="M31" s="42" t="n"/>
-      <c r="N31" s="42" t="n"/>
+      <c r="I31" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J31" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K31" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L31" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M31" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N31" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O31" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -7595,12 +8135,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I33" s="42" t="n"/>
-      <c r="J33" s="42" t="n"/>
-      <c r="K33" s="42" t="n"/>
-      <c r="L33" s="42" t="n"/>
-      <c r="M33" s="42" t="n"/>
-      <c r="N33" s="42" t="n"/>
+      <c r="I33" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J33" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K33" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L33" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M33" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N33" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O33" s="42" t="inlineStr">
         <is>
           <t>delete 200, get 404</t>
@@ -8052,12 +8612,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 201</t>
@@ -8104,12 +8684,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 415</t>
@@ -8156,12 +8756,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>HTTP 404</t>
@@ -8231,12 +8851,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="42" t="n"/>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
           <t>HTTP 201, 2 versions</t>
@@ -8305,12 +8945,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="42" t="n"/>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="42" t="n"/>
-      <c r="N18" s="42" t="n"/>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M18" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N18" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -8357,12 +9017,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-      <c r="N19" s="42" t="n"/>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
           <t>HTTP 200, 784 bytes</t>
@@ -8430,12 +9110,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="42" t="n"/>
-      <c r="K21" s="42" t="n"/>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="n"/>
-      <c r="N21" s="42" t="n"/>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L21" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O21" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -8887,12 +9587,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 201</t>
@@ -8939,12 +9659,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 422, connections 1-&gt;1</t>
@@ -8991,12 +9731,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>HTTP 422</t>
@@ -9043,12 +9803,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -9096,12 +9876,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="42" t="n"/>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -9148,12 +9948,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="42" t="n"/>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="42" t="n"/>
-      <c r="N17" s="42" t="n"/>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L17" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
           <t>HTTP 200</t>
@@ -9222,12 +10042,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-      <c r="N19" s="42" t="n"/>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
           <t>HTTP 201</t>
@@ -9274,12 +10114,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I20" s="42" t="n"/>
-      <c r="J20" s="42" t="n"/>
-      <c r="K20" s="42" t="n"/>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="42" t="n"/>
-      <c r="N20" s="42" t="n"/>
+      <c r="I20" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J20" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K20" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L20" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M20" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N20" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
           <t>HTTP 422</t>
@@ -9732,12 +10592,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 201, list HTTP 200</t>
@@ -9784,12 +10664,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 404</t>
@@ -9836,12 +10736,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>HTTP 204</t>
@@ -9888,12 +10808,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
           <t>HTTP 404</t>
@@ -10418,12 +11358,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="42" t="n"/>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N12" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
           <t>HTTP 422</t>
@@ -10470,12 +11430,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="J13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
           <t>HTTP 409 MODELS_NOT_CONFIGURED, 0 runs</t>
@@ -10523,12 +11503,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="42" t="n"/>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M14" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O14" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10575,12 +11575,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="42" t="n"/>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M15" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10651,12 +11671,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="42" t="n"/>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="42" t="n"/>
-      <c r="N17" s="42" t="n"/>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L17" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M17" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N17" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10726,12 +11766,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-      <c r="N19" s="42" t="n"/>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M19" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N19" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10800,12 +11860,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="42" t="n"/>
-      <c r="K21" s="42" t="n"/>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="n"/>
-      <c r="N21" s="42" t="n"/>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L21" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M21" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N21" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O21" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10872,12 +11952,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
-      <c r="N23" s="42" t="n"/>
+      <c r="I23" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J23" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K23" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L23" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M23" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N23" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O23" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -10945,12 +12045,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I25" s="42" t="n"/>
-      <c r="J25" s="42" t="n"/>
-      <c r="K25" s="42" t="n"/>
-      <c r="L25" s="42" t="n"/>
-      <c r="M25" s="42" t="n"/>
-      <c r="N25" s="42" t="n"/>
+      <c r="I25" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J25" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K25" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L25" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M25" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N25" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O25" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -11018,12 +12138,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I27" s="42" t="n"/>
-      <c r="J27" s="42" t="n"/>
-      <c r="K27" s="42" t="n"/>
-      <c r="L27" s="42" t="n"/>
-      <c r="M27" s="42" t="n"/>
-      <c r="N27" s="42" t="n"/>
+      <c r="I27" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J27" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K27" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L27" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M27" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N27" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O27" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
@@ -11090,12 +12230,32 @@
           <t>Ngô Thành Đạt</t>
         </is>
       </c>
-      <c r="I29" s="42" t="n"/>
-      <c r="J29" s="42" t="n"/>
-      <c r="K29" s="42" t="n"/>
-      <c r="L29" s="42" t="n"/>
-      <c r="M29" s="42" t="n"/>
-      <c r="N29" s="42" t="n"/>
+      <c r="I29" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J29" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K29" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
+      <c r="L29" s="42" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M29" s="162" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N29" s="42" t="inlineStr">
+        <is>
+          <t>Ngô Thành Đạt</t>
+        </is>
+      </c>
       <c r="O29" s="42" t="inlineStr">
         <is>
           <t>Pending: no LLM provider is configured on the local stack (/admin/models stage and review are null), so no run can start; needs a provider key set by the Platform Admin</t>
